--- a/Estados_Financieros_Doner_Street_2026.xlsx
+++ b/Estados_Financieros_Doner_Street_2026.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1650,231 +1650,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ingresos financieros</t>
+          <t>Gastos financieros (4x1000)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>133333</v>
+        <v>317927</v>
       </c>
       <c r="C29" t="n">
-        <v>133333</v>
+        <v>431465</v>
       </c>
       <c r="D29" t="n">
-        <v>133333</v>
+        <v>400169</v>
       </c>
       <c r="E29" t="n">
-        <v>133333</v>
+        <v>453299</v>
       </c>
       <c r="F29" t="n">
-        <v>133333</v>
+        <v>464216</v>
       </c>
       <c r="G29" t="n">
-        <v>133333</v>
+        <v>341945</v>
       </c>
       <c r="H29" t="n">
-        <v>133333</v>
+        <v>285176</v>
       </c>
       <c r="I29" t="n">
-        <v>133333</v>
+        <v>459849</v>
       </c>
       <c r="J29" t="n">
-        <v>133333</v>
+        <v>453299</v>
       </c>
       <c r="K29" t="n">
-        <v>133333</v>
+        <v>464216</v>
       </c>
       <c r="L29" t="n">
-        <v>133333</v>
+        <v>448932</v>
       </c>
       <c r="M29" t="n">
-        <v>133337</v>
+        <v>285176</v>
       </c>
       <c r="N29" t="n">
-        <v>1600000</v>
+        <v>4805669</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Gastos financieros (4x1000)</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>317927</v>
-      </c>
-      <c r="C30" t="n">
-        <v>431465</v>
-      </c>
-      <c r="D30" t="n">
-        <v>400169</v>
-      </c>
-      <c r="E30" t="n">
-        <v>453299</v>
-      </c>
-      <c r="F30" t="n">
-        <v>464216</v>
-      </c>
-      <c r="G30" t="n">
-        <v>341945</v>
-      </c>
-      <c r="H30" t="n">
-        <v>285176</v>
-      </c>
-      <c r="I30" t="n">
-        <v>459849</v>
-      </c>
-      <c r="J30" t="n">
-        <v>453299</v>
-      </c>
-      <c r="K30" t="n">
-        <v>464216</v>
-      </c>
-      <c r="L30" t="n">
-        <v>448932</v>
-      </c>
-      <c r="M30" t="n">
-        <v>285176</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4805669</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Utilidad antes de impuestos</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-6465280</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>9207897</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4887727</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>12221970</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>13729007</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-3149801</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>-10986390</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>13126192</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>12221970</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>13729007</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>11619156</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>-10986382</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>59155073</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Utilidad antes de impuestos</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-6331947</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>9341230</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>5021060</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>12355303</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>13862340</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>-3016468</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>-10853057</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>13259525</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>12355303</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>13862340</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>11752489</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>-10853045</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>60755073</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Impuesto de renta (35% anual, provisionado)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1725356</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1725360</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20704276</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Impuesto de renta (35% anual, provisionado)</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1772023</v>
-      </c>
-      <c r="N32" t="n">
-        <v>21264276</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Utilidad neta</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>-8103970</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>7569207</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>3249037</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10583280</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>12090317</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>-4788491</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>-12625080</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>11487502</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>10583280</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>12090317</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>9980466</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>-12625068</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>39490797</v>
+      <c r="B32" s="3" t="n">
+        <v>-8190636</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>7482541</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>3162371</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>10496614</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>12003651</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-4875157</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>-12711746</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>11400836</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>10496614</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>12003651</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>9893800</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>-12711742</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>38450797</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2006,43 +1960,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-8103970</v>
+        <v>-8190636</v>
       </c>
       <c r="C3" t="n">
-        <v>7569207</v>
+        <v>7482541</v>
       </c>
       <c r="D3" t="n">
-        <v>3249037</v>
+        <v>3162371</v>
       </c>
       <c r="E3" t="n">
-        <v>10583280</v>
+        <v>10496614</v>
       </c>
       <c r="F3" t="n">
-        <v>12090317</v>
+        <v>12003651</v>
       </c>
       <c r="G3" t="n">
-        <v>-4788491</v>
+        <v>-4875157</v>
       </c>
       <c r="H3" t="n">
-        <v>-12625080</v>
+        <v>-12711746</v>
       </c>
       <c r="I3" t="n">
-        <v>11487502</v>
+        <v>11400836</v>
       </c>
       <c r="J3" t="n">
-        <v>10583280</v>
+        <v>10496614</v>
       </c>
       <c r="K3" t="n">
-        <v>12090317</v>
+        <v>12003651</v>
       </c>
       <c r="L3" t="n">
-        <v>9980466</v>
+        <v>9893800</v>
       </c>
       <c r="M3" t="n">
-        <v>-12625068</v>
+        <v>-12711742</v>
       </c>
       <c r="N3" t="n">
-        <v>39490797</v>
+        <v>38450797</v>
       </c>
     </row>
     <row r="4">
@@ -2094,57 +2048,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(+/-) Proveedores</t>
+          <t>(+/-) Nómina por pagar</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21364839</v>
+        <v>2578500</v>
       </c>
       <c r="C5" t="n">
-        <v>16266411</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-7121613</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7121613</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-12794625</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-7113520</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19422580</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>485565</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-501750</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-19406395</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>17723105</v>
+        <v>2578500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(+/-) Nómina por pagar</t>
+          <t>(+/-) Seguridad social por pagar</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2180,197 +2134,171 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(+/-) Seguridad social por pagar</t>
+          <t>(+/-) Impuestos por pagar</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3915500</v>
+        <v>6896677</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3796217</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-1105923</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1751605</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>322842</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-4185159</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1968109</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5865464</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-268373</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>322842</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-563979</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>15674991</v>
       </c>
       <c r="N7" t="n">
-        <v>3915500</v>
+        <v>26539095</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>(+/-) Impuestos por pagar</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6943344</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3842884</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-1059256</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1798272</v>
-      </c>
-      <c r="F8" t="n">
-        <v>369509</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-4138492</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-1921442</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5912131</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-221706</v>
-      </c>
-      <c r="K8" t="n">
-        <v>369509</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-517312</v>
-      </c>
-      <c r="M8" t="n">
-        <v>15721654</v>
-      </c>
-      <c r="N8" t="n">
-        <v>27099095</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo neto de operación</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6616708</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6201425</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3473115</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>13664886</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>13743160</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>-7643649</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-13263188</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>18682967</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>11644908</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>13743160</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>10746488</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>4379912</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>81989892</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>(+/-) Otras cuentas por pagar</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3500000</v>
-      </c>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVIDADES DE INVERSIÓN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Efectivo neto de operación</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>31614880</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>29095169</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>-3515165</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>20919832</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>13876493</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>-20304941</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>-20243375</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>38238880</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>12263806</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>13876493</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>10378071</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>-14893146</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>111306997</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Compra PP&amp;E + inventario apertura (enero)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-90000000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-90000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACTIVIDADES DE INVERSIÓN</t>
+          <t>ACTIVIDADES DE FINANCIACIÓN</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -2390,11 +2318,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Compra PP&amp;E + inventario apertura (enero)</t>
+          <t>Aporte de capital social (apertura, enero)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-90000000</v>
+        <v>130000000</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -2430,165 +2358,99 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-90000000</v>
+        <v>130000000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVIDADES DE FINANCIACIÓN</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Flujo neto del periodo</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46616708</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6201425</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>3473115</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>13664886</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>13743160</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-7643649</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-13263188</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>18682967</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>11644908</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>13743160</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>10746488</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>4379912</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>121989892</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Aporte de capital social (apertura, enero)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>130000000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Flujo neto del periodo</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>71614880</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>29095169</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>-3515165</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>20919832</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>13876493</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>-20304941</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-20243375</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>38238880</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>12263806</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>13876493</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>10378071</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>-14893146</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>151306997</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Saldo final de efectivo</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>71614880</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>100710049</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>97194884</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>118114716</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>131991209</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>111686268</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>91442893</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>129681773</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>141945579</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>155822072</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>166200143</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>151306997</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>151306997</v>
+      <c r="B14" s="3" t="n">
+        <v>46616708</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>52818133</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>56291248</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>69956134</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>83699294</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>76055645</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>62792457</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>81475424</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>93120332</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>106863492</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>117609980</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>121989892</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>121989892</v>
       </c>
     </row>
   </sheetData>
@@ -2602,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2720,43 +2582,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71614880</v>
+        <v>46616708</v>
       </c>
       <c r="C3" t="n">
-        <v>100710049</v>
+        <v>52818133</v>
       </c>
       <c r="D3" t="n">
-        <v>97194884</v>
+        <v>56291248</v>
       </c>
       <c r="E3" t="n">
-        <v>118114716</v>
+        <v>69956134</v>
       </c>
       <c r="F3" t="n">
-        <v>131991209</v>
+        <v>83699294</v>
       </c>
       <c r="G3" t="n">
-        <v>111686268</v>
+        <v>76055645</v>
       </c>
       <c r="H3" t="n">
-        <v>91442893</v>
+        <v>62792457</v>
       </c>
       <c r="I3" t="n">
-        <v>129681773</v>
+        <v>81475424</v>
       </c>
       <c r="J3" t="n">
-        <v>141945579</v>
+        <v>93120332</v>
       </c>
       <c r="K3" t="n">
-        <v>155822072</v>
+        <v>106863492</v>
       </c>
       <c r="L3" t="n">
-        <v>166200143</v>
+        <v>117609980</v>
       </c>
       <c r="M3" t="n">
-        <v>151306997</v>
+        <v>121989892</v>
       </c>
       <c r="N3" t="n">
-        <v>151306997</v>
+        <v>121989892</v>
       </c>
     </row>
     <row r="4">
@@ -2812,43 +2674,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>76614880</v>
+        <v>51616708</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>105710049</v>
+        <v>57818133</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>102194884</v>
+        <v>61291248</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>123114716</v>
+        <v>74956134</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>136991209</v>
+        <v>88699294</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>116686268</v>
+        <v>81055645</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>96442893</v>
+        <v>67792457</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>134681773</v>
+        <v>86475424</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>146945579</v>
+        <v>98120332</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>160822072</v>
+        <v>111863492</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>171200143</v>
+        <v>122609980</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>156306997</v>
+        <v>126989892</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>156306997</v>
+        <v>126989892</v>
       </c>
     </row>
     <row r="6">
@@ -2970,43 +2832,43 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>160198213</v>
+        <v>135200041</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>187876715</v>
+        <v>139984799</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>182944883</v>
+        <v>142041247</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>202448048</v>
+        <v>154289466</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>214907874</v>
+        <v>166615959</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>193186266</v>
+        <v>157555643</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>171526224</v>
+        <v>142875788</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>208348437</v>
+        <v>160142088</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>219195576</v>
+        <v>170370329</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>231655402</v>
+        <v>182696822</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>240616806</v>
+        <v>192026643</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>224306997</v>
+        <v>194989892</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>224306997</v>
+        <v>194989892</v>
       </c>
     </row>
     <row r="10">
@@ -3032,481 +2894,389 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Proveedores (15 días sobre insumos+CIF)</t>
+          <t>Nómina por pagar y prestaciones sociales</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21364839</v>
+        <v>2578500</v>
       </c>
       <c r="C11" t="n">
-        <v>37631250</v>
+        <v>2578500</v>
       </c>
       <c r="D11" t="n">
-        <v>30509637</v>
+        <v>2578500</v>
       </c>
       <c r="E11" t="n">
-        <v>37631250</v>
+        <v>2578500</v>
       </c>
       <c r="F11" t="n">
-        <v>37631250</v>
+        <v>2578500</v>
       </c>
       <c r="G11" t="n">
-        <v>24836625</v>
+        <v>2578500</v>
       </c>
       <c r="H11" t="n">
-        <v>17723105</v>
+        <v>2578500</v>
       </c>
       <c r="I11" t="n">
-        <v>37145685</v>
+        <v>2578500</v>
       </c>
       <c r="J11" t="n">
-        <v>37631250</v>
+        <v>2578500</v>
       </c>
       <c r="K11" t="n">
-        <v>37631250</v>
+        <v>2578500</v>
       </c>
       <c r="L11" t="n">
-        <v>37129500</v>
+        <v>2578500</v>
       </c>
       <c r="M11" t="n">
-        <v>17723105</v>
+        <v>2578500</v>
       </c>
       <c r="N11" t="n">
-        <v>17723105</v>
+        <v>2578500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nómina por pagar y prestaciones sociales</t>
+          <t>Seguridad social y parafiscales por pagar</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="C12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="D12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="E12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="F12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="G12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="H12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="I12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="J12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="K12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="L12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="M12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
       <c r="N12" t="n">
-        <v>2578500</v>
+        <v>3915500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Seguridad social y parafiscales por pagar</t>
+          <t>Impuestos por pagar (incl. renta 100% a dic 31)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3915500</v>
+        <v>6896677</v>
       </c>
       <c r="C13" t="n">
-        <v>3915500</v>
+        <v>10692894</v>
       </c>
       <c r="D13" t="n">
-        <v>3915500</v>
+        <v>9586971</v>
       </c>
       <c r="E13" t="n">
-        <v>3915500</v>
+        <v>11338576</v>
       </c>
       <c r="F13" t="n">
-        <v>3915500</v>
+        <v>11661418</v>
       </c>
       <c r="G13" t="n">
-        <v>3915500</v>
+        <v>7476259</v>
       </c>
       <c r="H13" t="n">
-        <v>3915500</v>
+        <v>5508150</v>
       </c>
       <c r="I13" t="n">
-        <v>3915500</v>
+        <v>11373614</v>
       </c>
       <c r="J13" t="n">
-        <v>3915500</v>
+        <v>11105241</v>
       </c>
       <c r="K13" t="n">
-        <v>3915500</v>
+        <v>11428083</v>
       </c>
       <c r="L13" t="n">
-        <v>3915500</v>
+        <v>10864104</v>
       </c>
       <c r="M13" t="n">
-        <v>3915500</v>
+        <v>26539095</v>
       </c>
       <c r="N13" t="n">
-        <v>3915500</v>
+        <v>26539095</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Impuestos por pagar (incl. renta 100% a dic 31)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>6943344</v>
-      </c>
-      <c r="C14" t="n">
-        <v>10786228</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9726972</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11525244</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11894753</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7756261</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5834819</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11746950</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11525244</v>
-      </c>
-      <c r="K14" t="n">
-        <v>11894753</v>
-      </c>
-      <c r="L14" t="n">
-        <v>11377441</v>
-      </c>
-      <c r="M14" t="n">
-        <v>27099095</v>
-      </c>
-      <c r="N14" t="n">
-        <v>27099095</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL PASIVO</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>13390677</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>10692894</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>9586971</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>11338576</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11661418</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>7476259</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>5508150</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>11373614</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>11105241</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11428083</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>10864104</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>26539095</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>26539095</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Otras cuentas por pagar (servicios del mes)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3500000</v>
-      </c>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PATRIMONIO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PASIVO</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>38302183</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>58411478</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>50230609</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>59150494</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>59520003</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>42586886</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>33551924</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>58886635</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>59150494</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>59520003</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>58500941</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>54816200</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>54816200</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Capital social (100% equity, apertura)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>130000000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>PATRIMONIO</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Utilidades retenidas (acumuladas del año)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-8190636</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-708095</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2454276</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12950890</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24954541</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20079384</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7367638</v>
+      </c>
+      <c r="I17" t="n">
+        <v>18768474</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29265088</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41268739</v>
+      </c>
+      <c r="L17" t="n">
+        <v>51162539</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38450797</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38450797</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Capital social (100% equity, apertura)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="C18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="E18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="F18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="G18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="M18" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="N18" t="n">
-        <v>130000000</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL PATRIMONIO</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>121809364</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>129291905</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>132454276</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>142950890</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>154954541</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>150079384</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>137367638</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>148768474</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>159265088</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>171268739</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>181162539</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>168450797</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>168450797</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Utilidades retenidas (acumuladas del año)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-8103970</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-534763</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2714274</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13297554</v>
-      </c>
-      <c r="F19" t="n">
-        <v>25387871</v>
-      </c>
-      <c r="G19" t="n">
-        <v>20599380</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7974300</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19461802</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30045082</v>
-      </c>
-      <c r="K19" t="n">
-        <v>42135399</v>
-      </c>
-      <c r="L19" t="n">
-        <v>52115865</v>
-      </c>
-      <c r="M19" t="n">
-        <v>39490797</v>
-      </c>
-      <c r="N19" t="n">
-        <v>39490797</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PATRIMONIO</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>121896030</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>129465237</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>132714274</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>143297554</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>155387871</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>150599380</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>137974300</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>149461802</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>160045082</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>172135399</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>182115865</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>169490797</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>169490797</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>TOTAL PASIVO + PATRIMONIO</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>160198213</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>187876715</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>182944883</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>202448048</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>214907874</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>193186266</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>171526224</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>208348437</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>219195576</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>231655402</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>240616806</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>224306997</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>224306997</v>
+      <c r="B19" s="3" t="n">
+        <v>135200041</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>139984799</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>142041247</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>154289466</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>166615959</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>157555643</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>142875788</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>160142088</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>170370329</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>182696822</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>192026643</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>194989892</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>194989892</v>
       </c>
     </row>
   </sheetData>
